--- a/SGC-CKN/Excel/dd4045ae-8df3-4413-ac2c-d456279fca5e_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-76_D800_15-03-2026.xlsx
+++ b/SGC-CKN/Excel/dd4045ae-8df3-4413-ac2c-d456279fca5e_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-76_D800_15-03-2026.xlsx
@@ -17,7 +17,7 @@
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P11-76</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t/>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t>SGCT-KCN0003</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">09:00
@@ -106,10 +106,13 @@
 15/03/2026</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">11:30
@@ -119,7 +122,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét- đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">12:30
@@ -139,9 +142,6 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
-  </si>
-  <si>
     <t xml:space="preserve">14:30
 15/03/2026</t>
   </si>
@@ -149,7 +149,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">15:30
@@ -159,7 +159,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">16:30
@@ -172,7 +172,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">17:00
@@ -1160,24 +1160,24 @@
         <v>5.64</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>-2.78</v>
@@ -1195,24 +1195,24 @@
         <v>4.7</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="13">
         <v>-12.96</v>
@@ -1230,24 +1230,24 @@
         <v>5.24</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="16">
         <v>-18.2</v>
@@ -1265,21 +1265,21 @@
         <v>12.76</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E15" s="21" t="s">
         <v>41</v>
@@ -1300,7 +1300,7 @@
         <v>5.45</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1335,7 +1335,7 @@
         <v>3.06</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1405,7 +1405,7 @@
         <v>9.4</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1580,7 +1580,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1609,7 +1609,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1638,7 +1638,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1667,7 +1667,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1780,10 +1780,10 @@
         <v>61</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>

--- a/SGC-CKN/Excel/dd4045ae-8df3-4413-ac2c-d456279fca5e_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-76_D800_15-03-2026.xlsx
+++ b/SGC-CKN/Excel/dd4045ae-8df3-4413-ac2c-d456279fca5e_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-76_D800_15-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
   <si>
     <t>Dự án</t>
   </si>
@@ -23,7 +23,7 @@
     <t>Hạng mục</t>
   </si>
   <si>
-    <t>Thi công cọc khoan nhồi đại trà_lô đất ký hiệu CT-02</t>
+    <t>Thi công cọc khoan nhồi, tường vây cho các hạng mục_Lô CT-02</t>
   </si>
   <si>
     <t>Tên bộ phận</t>
@@ -102,7 +102,7 @@
 15/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">09:20
+    <t xml:space="preserve">09:30
 15/03/2026</t>
   </si>
   <si>
@@ -135,24 +135,28 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">13:20
+    <t xml:space="preserve">13:30
 15/03/2026</t>
   </si>
   <si>
     <t>5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:30
+15/03/2026</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">14:30
 15/03/2026</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:30
+    <t xml:space="preserve">16:30
 15/03/2026</t>
   </si>
   <si>
@@ -162,7 +166,7 @@
     <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">16:30
+    <t xml:space="preserve">16:00
 15/03/2026</t>
   </si>
   <si>
@@ -325,7 +329,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -335,7 +339,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -1151,13 +1155,13 @@
         <v>-2.78</v>
       </c>
       <c r="H11" s="5">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="I11" s="5">
         <v>1.88</v>
       </c>
       <c r="J11" s="8">
-        <v>5.64</v>
+        <v>3.76</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1186,13 +1190,13 @@
         <v>-12.96</v>
       </c>
       <c r="H12" s="9">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="I12" s="9">
         <v>10.18</v>
       </c>
       <c r="J12" s="12">
-        <v>4.7</v>
+        <v>5.09</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1226,7 +1230,7 @@
       <c r="I13" s="13">
         <v>5.24</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="12">
         <v>5.24</v>
       </c>
       <c r="K13" s="14" t="s">
@@ -1256,13 +1260,13 @@
         <v>-28.83</v>
       </c>
       <c r="H14" s="16">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="I14" s="16">
         <v>10.63</v>
       </c>
-      <c r="J14" s="8">
-        <v>12.76</v>
+      <c r="J14" s="12">
+        <v>10.63</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1291,13 +1295,13 @@
         <v>-35.19</v>
       </c>
       <c r="H15" s="19">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="I15" s="19">
         <v>6.36</v>
       </c>
       <c r="J15" s="8">
-        <v>5.45</v>
+        <v>3.18</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1314,10 +1318,10 @@
         <v>43</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F16" s="22">
         <v>-35.19</v>
@@ -1326,13 +1330,13 @@
         <v>-38.25</v>
       </c>
       <c r="H16" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="22">
         <v>3.06</v>
       </c>
-      <c r="J16" s="12">
-        <v>3.06</v>
+      <c r="J16" s="8">
+        <v>1.53</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1340,19 +1344,19 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F17" s="25">
         <v>-38.25</v>
@@ -1361,33 +1365,33 @@
         <v>-45.2</v>
       </c>
       <c r="H17" s="25">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I17" s="25">
         <v>6.95</v>
       </c>
-      <c r="J17" s="8">
-        <v>6.95</v>
+      <c r="J17" s="12">
+        <v>13.9</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" s="28">
         <v>-45.2</v>
@@ -1401,7 +1405,7 @@
       <c r="I18" s="28">
         <v>4.7</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="12">
         <v>9.4</v>
       </c>
       <c r="K18" s="29" t="s">
@@ -1410,7 +1414,7 @@
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1516,31 +1520,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1563,13 +1567,13 @@
         <v>-2.78</v>
       </c>
       <c r="G2" s="5">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="H2" s="5">
         <v>1.88</v>
       </c>
       <c r="I2" s="8">
-        <v>5.64</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1592,13 +1596,13 @@
         <v>-12.96</v>
       </c>
       <c r="G3" s="9">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="H3" s="9">
         <v>10.18</v>
       </c>
       <c r="I3" s="12">
-        <v>4.7</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1626,7 +1630,7 @@
       <c r="H4" s="13">
         <v>5.24</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="12">
         <v>5.24</v>
       </c>
     </row>
@@ -1650,13 +1654,13 @@
         <v>-28.83</v>
       </c>
       <c r="G5" s="16">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="H5" s="16">
         <v>10.63</v>
       </c>
-      <c r="I5" s="8">
-        <v>12.76</v>
+      <c r="I5" s="12">
+        <v>10.63</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1679,13 +1683,13 @@
         <v>-35.19</v>
       </c>
       <c r="G6" s="19">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="H6" s="19">
         <v>6.36</v>
       </c>
       <c r="I6" s="8">
-        <v>5.45</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1708,13 +1712,13 @@
         <v>-38.25</v>
       </c>
       <c r="G7" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="22">
         <v>3.06</v>
       </c>
-      <c r="I7" s="12">
-        <v>3.06</v>
+      <c r="I7" s="8">
+        <v>1.53</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1725,7 +1729,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1737,13 +1741,13 @@
         <v>-45.2</v>
       </c>
       <c r="G8" s="25">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H8" s="25">
         <v>6.95</v>
       </c>
-      <c r="I8" s="8">
-        <v>6.95</v>
+      <c r="I8" s="12">
+        <v>13.9</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1754,7 +1758,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1771,13 +1775,13 @@
       <c r="H9" s="28">
         <v>4.7</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="12">
         <v>9.4</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>30</v>
@@ -1795,13 +1799,13 @@
         <v>-49.9</v>
       </c>
       <c r="G10" s="33">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="H10" s="33">
         <v>49</v>
       </c>
       <c r="I10" s="33">
-        <v>6.13</v>
+        <v>5.16</v>
       </c>
     </row>
   </sheetData>
